--- a/data/Processed/SQL Results Summary.xlsx
+++ b/data/Processed/SQL Results Summary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/434181ab9f802905/Desktop/Yvonne Portfolio/Superstore SQL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/434181ab9f802905/Desktop/Projects/Ecommerce_Sales_Analysis/data/Processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_F25DC773A252ABDACC104855495E516A5ADE58E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7C8F38A-22B3-4D14-BFE7-4D7557779BF8}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_F25DC773A252ABDACC104855495E516A5ADE58E1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AB45C4E0-C08C-4A71-8C17-9F2A4EE9F8D1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t>Adrian Barton</t>
   </si>
   <si>
-    <t>Low profit products with profit margin less than 10%</t>
-  </si>
-  <si>
     <t>Product Name</t>
   </si>
   <si>
@@ -1593,12 +1590,15 @@
   </si>
   <si>
     <t>Top 5 customers by sales</t>
+  </si>
+  <si>
+    <t>Low profit products with profit margin less than or equal to 10%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
@@ -1691,7 +1691,9 @@
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{F5EEF7CD-2CBB-4B98-8B23-E90972B3989A}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1977,7 +1979,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -2064,19 +2066,19 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>521</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -2084,10 +2086,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D3" s="5">
         <v>0.1</v>
@@ -2098,10 +2100,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D4" s="5">
         <v>0.1</v>
@@ -2112,10 +2114,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D5" s="5">
         <v>0.1</v>
@@ -2126,10 +2128,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D6" s="5">
         <v>0.1</v>
@@ -2140,10 +2142,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="5">
         <v>0.1</v>
@@ -2154,10 +2156,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D8" s="5">
         <v>9.9212597999999999E-2</v>
@@ -2168,10 +2170,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="5">
         <v>9.8387097000000007E-2</v>
@@ -2182,10 +2184,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D10" s="5">
         <v>9.4661921999999996E-2</v>
@@ -2196,10 +2198,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D11" s="5">
         <v>9.3046357999999996E-2</v>
@@ -2210,10 +2212,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" s="5">
         <v>9.2741934999999998E-2</v>
@@ -2224,10 +2226,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" s="5">
         <v>9.245283E-2</v>
@@ -2238,10 +2240,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D14" s="5">
         <v>9.1481937999999999E-2</v>
@@ -2252,10 +2254,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D15" s="5">
         <v>9.1228069999999994E-2</v>
@@ -2266,10 +2268,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" s="5">
         <v>9.0909090999999997E-2</v>
@@ -2280,10 +2282,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D17" s="5">
         <v>8.8888888999999999E-2</v>
@@ -2294,10 +2296,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D18" s="5">
         <v>8.8157895E-2</v>
@@ -2308,10 +2310,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D19" s="5">
         <v>8.8073393999999999E-2</v>
@@ -2322,10 +2324,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D20" s="5">
         <v>8.7719298000000001E-2</v>
@@ -2336,10 +2338,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D21" s="5">
         <v>8.7499999999999994E-2</v>
@@ -2350,10 +2352,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22" s="5">
         <v>8.7499999999999994E-2</v>
@@ -2364,10 +2366,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D23" s="5">
         <v>8.7499999999999994E-2</v>
@@ -2378,10 +2380,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" s="5">
         <v>8.7499999999999994E-2</v>
@@ -2392,10 +2394,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D25" s="5">
         <v>8.7499999999999994E-2</v>
@@ -2406,10 +2408,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D26" s="5">
         <v>8.7368421000000002E-2</v>
@@ -2420,10 +2422,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D27" s="5">
         <v>8.6792453000000006E-2</v>
@@ -2434,10 +2436,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D28" s="5">
         <v>8.6538461999999997E-2</v>
@@ -2448,10 +2450,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D29" s="5">
         <v>8.5245901999999998E-2</v>
@@ -2462,10 +2464,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D30" s="5">
         <v>8.4337349000000006E-2</v>
@@ -2476,10 +2478,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D31" s="5">
         <v>8.3606556999999998E-2</v>
@@ -2490,10 +2492,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D32" s="5">
         <v>8.3333332999999996E-2</v>
@@ -2504,10 +2506,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D33" s="5">
         <v>8.3333332999999996E-2</v>
@@ -2518,10 +2520,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D34" s="5">
         <v>8.1923076999999997E-2</v>
@@ -2532,10 +2534,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D35" s="5">
         <v>0.08</v>
@@ -2546,10 +2548,10 @@
         <v>34</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D36" s="5">
         <v>7.9629630000000007E-2</v>
@@ -2560,10 +2562,10 @@
         <v>35</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D37" s="5">
         <v>7.9279278999999994E-2</v>
@@ -2574,10 +2576,10 @@
         <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D38" s="5">
         <v>7.8787879000000005E-2</v>
@@ -2588,10 +2590,10 @@
         <v>37</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D39" s="5">
         <v>7.8181818E-2</v>
@@ -2602,10 +2604,10 @@
         <v>38</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D40" s="5">
         <v>7.6923077000000006E-2</v>
@@ -2616,10 +2618,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D41" s="5">
         <v>7.4999999999999997E-2</v>
@@ -2630,10 +2632,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D42" s="5">
         <v>7.4999999999999997E-2</v>
@@ -2644,10 +2646,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D43" s="5">
         <v>7.4999999999999997E-2</v>
@@ -2658,10 +2660,10 @@
         <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D44" s="5">
         <v>7.4999999999999997E-2</v>
@@ -2672,10 +2674,10 @@
         <v>43</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D45" s="5">
         <v>7.4999999999999997E-2</v>
@@ -2686,10 +2688,10 @@
         <v>44</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D46" s="5">
         <v>7.4999999999999997E-2</v>
@@ -2700,10 +2702,10 @@
         <v>45</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D47" s="5">
         <v>7.4999999999999997E-2</v>
@@ -2714,10 +2716,10 @@
         <v>46</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D48" s="5">
         <v>7.4999999999999997E-2</v>
@@ -2728,10 +2730,10 @@
         <v>47</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D49" s="5">
         <v>7.4999999999999997E-2</v>
@@ -2742,10 +2744,10 @@
         <v>48</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D50" s="5">
         <v>7.4647886999999996E-2</v>
@@ -2756,10 +2758,10 @@
         <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D51" s="5">
         <v>7.3359072999999997E-2</v>
@@ -2770,10 +2772,10 @@
         <v>50</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D52" s="5">
         <v>7.3267326999999993E-2</v>
@@ -2784,10 +2786,10 @@
         <v>51</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D53" s="5">
         <v>7.2868216999999999E-2</v>
@@ -2798,10 +2800,10 @@
         <v>52</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D54" s="5">
         <v>7.1428570999999996E-2</v>
@@ -2812,10 +2814,10 @@
         <v>53</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D55" s="5">
         <v>7.1428570999999996E-2</v>
@@ -2826,10 +2828,10 @@
         <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D56" s="5">
         <v>7.1428570999999996E-2</v>
@@ -2840,10 +2842,10 @@
         <v>55</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D57" s="5">
         <v>7.0048309000000003E-2</v>
@@ -2854,10 +2856,10 @@
         <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D58" s="5">
         <v>7.0000000000000007E-2</v>
@@ -2868,10 +2870,10 @@
         <v>57</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D59" s="5">
         <v>6.8235294000000002E-2</v>
@@ -2882,10 +2884,10 @@
         <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D60" s="5">
         <v>6.8047336999999999E-2</v>
@@ -2896,10 +2898,10 @@
         <v>59</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D61" s="5">
         <v>6.7372880999999996E-2</v>
@@ -2910,10 +2912,10 @@
         <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D62" s="5">
         <v>6.7073171000000001E-2</v>
@@ -2924,10 +2926,10 @@
         <v>61</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D63" s="5">
         <v>6.6666666999999999E-2</v>
@@ -2938,10 +2940,10 @@
         <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D64" s="5">
         <v>6.6666666999999999E-2</v>
@@ -2952,10 +2954,10 @@
         <v>63</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D65" s="5">
         <v>6.6666666999999999E-2</v>
@@ -2966,10 +2968,10 @@
         <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D66" s="5">
         <v>6.6363636000000004E-2</v>
@@ -2980,10 +2982,10 @@
         <v>65</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D67" s="5">
         <v>6.6279069999999995E-2</v>
@@ -2994,10 +2996,10 @@
         <v>66</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D68" s="5">
         <v>6.6279069999999995E-2</v>
@@ -3008,10 +3010,10 @@
         <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D69" s="5">
         <v>6.6079294999999996E-2</v>
@@ -3022,10 +3024,10 @@
         <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D70" s="5">
         <v>6.5945946000000005E-2</v>
@@ -3036,10 +3038,10 @@
         <v>69</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D71" s="5">
         <v>6.5789474000000001E-2</v>
@@ -3050,10 +3052,10 @@
         <v>70</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D72" s="5">
         <v>6.5656566E-2</v>
@@ -3064,10 +3066,10 @@
         <v>71</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D73" s="5">
         <v>6.5602836999999997E-2</v>
@@ -3078,10 +3080,10 @@
         <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D74" s="5">
         <v>6.5420561000000002E-2</v>
@@ -3092,10 +3094,10 @@
         <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D75" s="5">
         <v>6.5126050000000005E-2</v>
@@ -3106,10 +3108,10 @@
         <v>74</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D76" s="5">
         <v>6.4367815999999994E-2</v>
@@ -3120,10 +3122,10 @@
         <v>75</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D77" s="5">
         <v>6.4327485000000004E-2</v>
@@ -3134,10 +3136,10 @@
         <v>76</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D78" s="5">
         <v>6.4000000000000001E-2</v>
@@ -3148,10 +3150,10 @@
         <v>77</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D79" s="5">
         <v>6.3970587999999995E-2</v>
@@ -3162,10 +3164,10 @@
         <v>78</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D80" s="5">
         <v>6.3440860000000002E-2</v>
@@ -3176,10 +3178,10 @@
         <v>79</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D81" s="5">
         <v>6.25E-2</v>
@@ -3190,10 +3192,10 @@
         <v>80</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D82" s="5">
         <v>6.1971830999999998E-2</v>
@@ -3204,10 +3206,10 @@
         <v>81</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D83" s="5">
         <v>6.1874999999999999E-2</v>
@@ -3218,10 +3220,10 @@
         <v>82</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D84" s="5">
         <v>6.1111111000000003E-2</v>
@@ -3232,10 +3234,10 @@
         <v>83</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D85" s="5">
         <v>6.097561E-2</v>
@@ -3246,10 +3248,10 @@
         <v>84</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D86" s="5">
         <v>6.0869565E-2</v>
@@ -3260,10 +3262,10 @@
         <v>85</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D87" s="5">
         <v>6.0869565E-2</v>
@@ -3274,10 +3276,10 @@
         <v>86</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D88" s="5">
         <v>6.0294118000000001E-2</v>
@@ -3288,10 +3290,10 @@
         <v>87</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D89" s="5">
         <v>0.06</v>
@@ -3302,10 +3304,10 @@
         <v>88</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D90" s="5">
         <v>5.9848485E-2</v>
@@ -3316,10 +3318,10 @@
         <v>89</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D91" s="5">
         <v>5.8706467999999998E-2</v>
@@ -3330,10 +3332,10 @@
         <v>90</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D92" s="5">
         <v>5.8163264999999999E-2</v>
@@ -3344,10 +3346,10 @@
         <v>91</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D93" s="5">
         <v>5.8064515999999997E-2</v>
@@ -3358,10 +3360,10 @@
         <v>92</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D94" s="5">
         <v>5.7692307999999998E-2</v>
@@ -3372,10 +3374,10 @@
         <v>93</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D95" s="5">
         <v>5.5870444999999998E-2</v>
@@ -3386,10 +3388,10 @@
         <v>94</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D96" s="5">
         <v>5.5357142999999998E-2</v>
@@ -3400,10 +3402,10 @@
         <v>95</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D97" s="5">
         <v>5.5241934999999999E-2</v>
@@ -3414,10 +3416,10 @@
         <v>96</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D98" s="5">
         <v>5.4621849E-2</v>
@@ -3428,10 +3430,10 @@
         <v>97</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D99" s="5">
         <v>5.4545455E-2</v>
@@ -3442,10 +3444,10 @@
         <v>98</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D100" s="5">
         <v>5.4545455E-2</v>
@@ -3456,10 +3458,10 @@
         <v>99</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D101" s="5">
         <v>5.4054053999999997E-2</v>
@@ -3470,10 +3472,10 @@
         <v>100</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D102" s="5">
         <v>5.3488371999999999E-2</v>
@@ -3484,10 +3486,10 @@
         <v>101</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D103" s="5">
         <v>5.3333332999999997E-2</v>
@@ -3498,10 +3500,10 @@
         <v>102</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D104" s="5">
         <v>5.1234568000000001E-2</v>
@@ -3512,10 +3514,10 @@
         <v>103</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D105" s="5">
         <v>5.0034269999999999E-2</v>
@@ -3526,10 +3528,10 @@
         <v>104</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D106" s="5">
         <v>0.05</v>
@@ -3540,10 +3542,10 @@
         <v>105</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D107" s="5">
         <v>4.8991354000000001E-2</v>
@@ -3554,10 +3556,10 @@
         <v>106</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D108" s="5">
         <v>4.8458149999999998E-2</v>
@@ -3568,10 +3570,10 @@
         <v>107</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D109" s="5">
         <v>4.8275862000000003E-2</v>
@@ -3582,10 +3584,10 @@
         <v>108</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D110" s="5">
         <v>4.6511627999999999E-2</v>
@@ -3596,10 +3598,10 @@
         <v>109</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D111" s="5">
         <v>4.6242775E-2</v>
@@ -3610,10 +3612,10 @@
         <v>110</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D112" s="5">
         <v>4.5744681000000002E-2</v>
@@ -3624,10 +3626,10 @@
         <v>111</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D113" s="5">
         <v>4.5454544999999999E-2</v>
@@ -3638,10 +3640,10 @@
         <v>112</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D114" s="5">
         <v>4.4630872000000002E-2</v>
@@ -3652,10 +3654,10 @@
         <v>113</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D115" s="5">
         <v>4.4626168000000001E-2</v>
@@ -3666,10 +3668,10 @@
         <v>114</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D116" s="5">
         <v>4.4382022E-2</v>
@@ -3680,10 +3682,10 @@
         <v>115</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D117" s="5">
         <v>4.4247788000000003E-2</v>
@@ -3694,10 +3696,10 @@
         <v>116</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D118" s="5">
         <v>4.4099379000000001E-2</v>
@@ -3708,10 +3710,10 @@
         <v>117</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D119" s="5">
         <v>4.3949044999999999E-2</v>
@@ -3722,10 +3724,10 @@
         <v>118</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D120" s="5">
         <v>4.2999999999999997E-2</v>
@@ -3736,10 +3738,10 @@
         <v>119</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D121" s="5">
         <v>4.2857143E-2</v>
@@ -3750,10 +3752,10 @@
         <v>120</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D122" s="5">
         <v>4.2352940999999998E-2</v>
@@ -3764,10 +3766,10 @@
         <v>121</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D123" s="5">
         <v>4.1782729999999997E-2</v>
@@ -3778,10 +3780,10 @@
         <v>122</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D124" s="5">
         <v>4.1538461999999998E-2</v>
@@ -3792,10 +3794,10 @@
         <v>123</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D125" s="5">
         <v>4.0948275999999999E-2</v>
@@ -3806,10 +3808,10 @@
         <v>124</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D126" s="5">
         <v>4.0948275999999999E-2</v>
@@ -3820,10 +3822,10 @@
         <v>125</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D127" s="5">
         <v>4.0867992999999998E-2</v>
@@ -3834,10 +3836,10 @@
         <v>126</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D128" s="5">
         <v>0.04</v>
@@ -3848,10 +3850,10 @@
         <v>127</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D129" s="5">
         <v>0.04</v>
@@ -3862,10 +3864,10 @@
         <v>128</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D130" s="5">
         <v>0.04</v>
@@ -3876,10 +3878,10 @@
         <v>129</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D131" s="5">
         <v>3.8743455000000003E-2</v>
@@ -3890,10 +3892,10 @@
         <v>130</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D132" s="5">
         <v>3.7974684000000002E-2</v>
@@ -3904,10 +3906,10 @@
         <v>131</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D133" s="5">
         <v>3.7931034000000002E-2</v>
@@ -3918,10 +3920,10 @@
         <v>132</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D134" s="5">
         <v>3.7931034000000002E-2</v>
@@ -3932,10 +3934,10 @@
         <v>133</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D135" s="5">
         <v>3.5714285999999998E-2</v>
@@ -3946,10 +3948,10 @@
         <v>134</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D136" s="5">
         <v>3.515625E-2</v>
@@ -3960,10 +3962,10 @@
         <v>135</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D137" s="5">
         <v>3.4782608999999999E-2</v>
@@ -3974,10 +3976,10 @@
         <v>136</v>
       </c>
       <c r="B138" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D138" s="5">
         <v>3.4782608999999999E-2</v>
@@ -3988,10 +3990,10 @@
         <v>137</v>
       </c>
       <c r="B139" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D139" s="5">
         <v>3.3561644000000002E-2</v>
@@ -4002,10 +4004,10 @@
         <v>138</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D140" s="5">
         <v>3.2500000000000001E-2</v>
@@ -4016,10 +4018,10 @@
         <v>139</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D141" s="5">
         <v>3.2352941000000003E-2</v>
@@ -4030,10 +4032,10 @@
         <v>140</v>
       </c>
       <c r="B142" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D142" s="5">
         <v>3.2307691999999999E-2</v>
@@ -4044,10 +4046,10 @@
         <v>141</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D143" s="5">
         <v>3.2258065000000002E-2</v>
@@ -4058,10 +4060,10 @@
         <v>142</v>
       </c>
       <c r="B144" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D144" s="5">
         <v>3.1944444000000002E-2</v>
@@ -4072,10 +4074,10 @@
         <v>143</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D145" s="5">
         <v>3.1944444000000002E-2</v>
@@ -4086,10 +4088,10 @@
         <v>144</v>
       </c>
       <c r="B146" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D146" s="5">
         <v>3.1632652999999997E-2</v>
@@ -4100,10 +4102,10 @@
         <v>145</v>
       </c>
       <c r="B147" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D147" s="5">
         <v>3.0097087000000002E-2</v>
@@ -4114,10 +4116,10 @@
         <v>146</v>
       </c>
       <c r="B148" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D148" s="5">
         <v>0.03</v>
@@ -4128,10 +4130,10 @@
         <v>147</v>
       </c>
       <c r="B149" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D149" s="5">
         <v>2.9870130000000002E-2</v>
@@ -4142,10 +4144,10 @@
         <v>148</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D150" s="5">
         <v>2.8571428999999999E-2</v>
@@ -4156,10 +4158,10 @@
         <v>149</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D151" s="5">
         <v>2.7777777999999999E-2</v>
@@ -4170,10 +4172,10 @@
         <v>150</v>
       </c>
       <c r="B152" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D152" s="5">
         <v>2.7027026999999999E-2</v>
@@ -4184,10 +4186,10 @@
         <v>151</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D153" s="5">
         <v>2.6639343999999999E-2</v>
@@ -4198,10 +4200,10 @@
         <v>152</v>
       </c>
       <c r="B154" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D154" s="5">
         <v>2.6315788999999999E-2</v>
@@ -4212,10 +4214,10 @@
         <v>153</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D155" s="5">
         <v>2.6229507999999999E-2</v>
@@ -4226,10 +4228,10 @@
         <v>154</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D156" s="5">
         <v>2.5000000000000001E-2</v>
@@ -4240,10 +4242,10 @@
         <v>155</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D157" s="5">
         <v>2.5000000000000001E-2</v>
@@ -4254,10 +4256,10 @@
         <v>156</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D158" s="5">
         <v>2.5000000000000001E-2</v>
@@ -4268,10 +4270,10 @@
         <v>157</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D159" s="5">
         <v>2.4390243999999998E-2</v>
@@ -4282,10 +4284,10 @@
         <v>158</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D160" s="5">
         <v>2.3033708E-2</v>
@@ -4296,10 +4298,10 @@
         <v>159</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D161" s="5">
         <v>2.2727272999999999E-2</v>
@@ -4310,10 +4312,10 @@
         <v>160</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D162" s="5">
         <v>2.2222222E-2</v>
@@ -4324,10 +4326,10 @@
         <v>161</v>
       </c>
       <c r="B163" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D163" s="5">
         <v>2.1739129999999999E-2</v>
@@ -4338,10 +4340,10 @@
         <v>162</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D164" s="5">
         <v>2.1739129999999999E-2</v>
@@ -4352,10 +4354,10 @@
         <v>163</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D165" s="5">
         <v>0.02</v>
@@ -4366,10 +4368,10 @@
         <v>164</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D166" s="5">
         <v>1.9607843E-2</v>
@@ -4380,10 +4382,10 @@
         <v>165</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D167" s="5">
         <v>1.9230769000000002E-2</v>
@@ -4394,10 +4396,10 @@
         <v>166</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D168" s="5">
         <v>1.9230769000000002E-2</v>
@@ -4408,10 +4410,10 @@
         <v>167</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D169" s="5">
         <v>1.9230769000000002E-2</v>
@@ -4422,10 +4424,10 @@
         <v>168</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D170" s="5">
         <v>1.8556700999999998E-2</v>
@@ -4436,10 +4438,10 @@
         <v>169</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D171" s="5">
         <v>1.8487395E-2</v>
@@ -4450,10 +4452,10 @@
         <v>170</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D172" s="5">
         <v>1.8367346999999999E-2</v>
@@ -4464,10 +4466,10 @@
         <v>171</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D173" s="5">
         <v>1.8181817999999999E-2</v>
@@ -4478,10 +4480,10 @@
         <v>172</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D174" s="5">
         <v>1.6E-2</v>
@@ -4492,10 +4494,10 @@
         <v>173</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D175" s="5">
         <v>1.5238095E-2</v>
@@ -4506,10 +4508,10 @@
         <v>174</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D176" s="5">
         <v>1.5151515000000001E-2</v>
@@ -4520,10 +4522,10 @@
         <v>175</v>
       </c>
       <c r="B177" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D177" s="5">
         <v>1.4E-2</v>
@@ -4534,10 +4536,10 @@
         <v>176</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D178" s="5">
         <v>1.2500000000000001E-2</v>
@@ -4548,10 +4550,10 @@
         <v>177</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D179" s="5">
         <v>1.2500000000000001E-2</v>
@@ -4562,10 +4564,10 @@
         <v>178</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D180" s="5">
         <v>1.1764706E-2</v>
@@ -4576,10 +4578,10 @@
         <v>179</v>
       </c>
       <c r="B181" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D181" s="5">
         <v>1.1764706E-2</v>
@@ -4590,10 +4592,10 @@
         <v>180</v>
       </c>
       <c r="B182" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D182" s="5">
         <v>0.01</v>
@@ -4604,10 +4606,10 @@
         <v>181</v>
       </c>
       <c r="B183" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D183" s="5">
         <v>9.3023259999999997E-3</v>
@@ -4618,10 +4620,10 @@
         <v>182</v>
       </c>
       <c r="B184" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D184" s="5">
         <v>9.1743120000000004E-3</v>
@@ -4632,10 +4634,10 @@
         <v>183</v>
       </c>
       <c r="B185" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D185" s="5">
         <v>9.0322579999999996E-3</v>
@@ -4646,10 +4648,10 @@
         <v>184</v>
       </c>
       <c r="B186" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D186" s="5">
         <v>8.1632649999999994E-3</v>
@@ -4660,10 +4662,10 @@
         <v>185</v>
       </c>
       <c r="B187" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D187" s="5">
         <v>7.9545450000000004E-3</v>
@@ -4674,10 +4676,10 @@
         <v>186</v>
       </c>
       <c r="B188" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D188" s="5">
         <v>7.6923080000000001E-3</v>
@@ -4688,10 +4690,10 @@
         <v>187</v>
       </c>
       <c r="B189" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D189" s="5">
         <v>5.7692309999999997E-3</v>
@@ -4702,10 +4704,10 @@
         <v>188</v>
       </c>
       <c r="B190" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D190" s="5">
         <v>5.1020409999999999E-3</v>
@@ -4716,10 +4718,10 @@
         <v>189</v>
       </c>
       <c r="B191" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D191" s="5">
         <v>4.2372879999999996E-3</v>
@@ -4730,10 +4732,10 @@
         <v>190</v>
       </c>
       <c r="B192" s="4" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D192" s="5">
         <v>2.7397260000000001E-3</v>
@@ -4744,10 +4746,10 @@
         <v>191</v>
       </c>
       <c r="B193" s="4" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D193" s="5">
         <v>3.9E-18</v>
@@ -4758,10 +4760,10 @@
         <v>192</v>
       </c>
       <c r="B194" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D194" s="5">
         <v>0</v>
@@ -4772,10 +4774,10 @@
         <v>193</v>
       </c>
       <c r="B195" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D195" s="5">
         <v>0</v>
@@ -4786,10 +4788,10 @@
         <v>194</v>
       </c>
       <c r="B196" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D196" s="5">
         <v>-1.34E-18</v>
@@ -4800,10 +4802,10 @@
         <v>195</v>
       </c>
       <c r="B197" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D197" s="5">
         <v>-1.8600000000000001E-18</v>
@@ -4814,10 +4816,10 @@
         <v>196</v>
       </c>
       <c r="B198" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D198" s="5">
         <v>-1.13E-17</v>
@@ -4828,10 +4830,10 @@
         <v>197</v>
       </c>
       <c r="B199" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D199" s="5">
         <v>-1.0695189999999999E-3</v>
@@ -4842,10 +4844,10 @@
         <v>198</v>
       </c>
       <c r="B200" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D200" s="5">
         <v>-1.73913E-3</v>
@@ -4856,10 +4858,10 @@
         <v>199</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D201" s="5">
         <v>-2.5641029999999999E-3</v>
@@ -4870,10 +4872,10 @@
         <v>200</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D202" s="5">
         <v>-3.4482760000000001E-3</v>
@@ -4884,10 +4886,10 @@
         <v>201</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D203" s="5">
         <v>-5.1282050000000003E-3</v>
@@ -4898,10 +4900,10 @@
         <v>202</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D204" s="5">
         <v>-5.2795029999999996E-3</v>
@@ -4912,10 +4914,10 @@
         <v>203</v>
       </c>
       <c r="B205" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D205" s="5">
         <v>-5.9880239999999998E-3</v>
@@ -4926,10 +4928,10 @@
         <v>204</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D206" s="5">
         <v>-7.0000000000000001E-3</v>
@@ -4940,10 +4942,10 @@
         <v>205</v>
       </c>
       <c r="B207" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D207" s="5">
         <v>-8.3333330000000001E-3</v>
@@ -4954,10 +4956,10 @@
         <v>206</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D208" s="5">
         <v>-8.4745759999999993E-3</v>
@@ -4968,10 +4970,10 @@
         <v>207</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D209" s="5">
         <v>-8.9686100000000001E-3</v>
@@ -4982,10 +4984,10 @@
         <v>208</v>
       </c>
       <c r="B210" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D210" s="5">
         <v>-9.0909089999999994E-3</v>
@@ -4996,10 +4998,10 @@
         <v>209</v>
       </c>
       <c r="B211" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D211" s="5">
         <v>-9.7560979999999995E-3</v>
@@ -5010,10 +5012,10 @@
         <v>210</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D212" s="5">
         <v>-1.0416666999999999E-2</v>
@@ -5024,10 +5026,10 @@
         <v>211</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D213" s="5">
         <v>-1.1518324999999999E-2</v>
@@ -5038,10 +5040,10 @@
         <v>212</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D214" s="5">
         <v>-1.1570248E-2</v>
@@ -5052,10 +5054,10 @@
         <v>213</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D215" s="5">
         <v>-1.3888889E-2</v>
@@ -5066,10 +5068,10 @@
         <v>214</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D216" s="5">
         <v>-1.396648E-2</v>
@@ -5080,10 +5082,10 @@
         <v>215</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D217" s="5">
         <v>-1.4221861000000001E-2</v>
@@ -5094,10 +5096,10 @@
         <v>216</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D218" s="5">
         <v>-1.4847162000000001E-2</v>
@@ -5108,10 +5110,10 @@
         <v>217</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D219" s="5">
         <v>-1.5238095E-2</v>
@@ -5122,10 +5124,10 @@
         <v>218</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D220" s="5">
         <v>-1.5384615000000001E-2</v>
@@ -5136,10 +5138,10 @@
         <v>219</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D221" s="5">
         <v>-1.5384615000000001E-2</v>
@@ -5150,10 +5152,10 @@
         <v>220</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D222" s="5">
         <v>-1.5384615000000001E-2</v>
@@ -5164,10 +5166,10 @@
         <v>221</v>
       </c>
       <c r="B223" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D223" s="5">
         <v>-1.5686275E-2</v>
@@ -5178,10 +5180,10 @@
         <v>222</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D224" s="5">
         <v>-1.6949153000000002E-2</v>
@@ -5192,10 +5194,10 @@
         <v>223</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D225" s="5">
         <v>-1.7179024000000001E-2</v>
@@ -5206,10 +5208,10 @@
         <v>224</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D226" s="5">
         <v>-1.7391304E-2</v>
@@ -5220,10 +5222,10 @@
         <v>225</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D227" s="5">
         <v>-1.7621145000000001E-2</v>
@@ -5234,10 +5236,10 @@
         <v>226</v>
       </c>
       <c r="B228" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D228" s="5">
         <v>-1.8181817999999999E-2</v>
@@ -5248,10 +5250,10 @@
         <v>227</v>
       </c>
       <c r="B229" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D229" s="5">
         <v>-1.8181817999999999E-2</v>
@@ -5262,10 +5264,10 @@
         <v>228</v>
       </c>
       <c r="B230" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D230" s="5">
         <v>-1.8867925000000001E-2</v>
@@ -5276,10 +5278,10 @@
         <v>229</v>
       </c>
       <c r="B231" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D231" s="5">
         <v>-1.9199999999999998E-2</v>
@@ -5290,10 +5292,10 @@
         <v>230</v>
       </c>
       <c r="B232" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D232" s="5">
         <v>-0.02</v>
@@ -5304,10 +5306,10 @@
         <v>231</v>
       </c>
       <c r="B233" s="4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D233" s="5">
         <v>-2.0689655000000001E-2</v>
@@ -5318,10 +5320,10 @@
         <v>232</v>
       </c>
       <c r="B234" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D234" s="5">
         <v>-2.1621622E-2</v>
@@ -5332,10 +5334,10 @@
         <v>233</v>
       </c>
       <c r="B235" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D235" s="5">
         <v>-2.1969697E-2</v>
@@ -5346,10 +5348,10 @@
         <v>234</v>
       </c>
       <c r="B236" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D236" s="5">
         <v>-2.2727272999999999E-2</v>
@@ -5360,10 +5362,10 @@
         <v>235</v>
       </c>
       <c r="B237" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D237" s="5">
         <v>-2.3142250999999999E-2</v>
@@ -5374,10 +5376,10 @@
         <v>236</v>
       </c>
       <c r="B238" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D238" s="5">
         <v>-2.4338624E-2</v>
@@ -5388,10 +5390,10 @@
         <v>237</v>
       </c>
       <c r="B239" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D239" s="5">
         <v>-2.4390243999999998E-2</v>
@@ -5402,10 +5404,10 @@
         <v>238</v>
       </c>
       <c r="B240" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D240" s="5">
         <v>-2.5180897000000001E-2</v>
@@ -5416,10 +5418,10 @@
         <v>239</v>
       </c>
       <c r="B241" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D241" s="5">
         <v>-2.5203251999999999E-2</v>
@@ -5430,10 +5432,10 @@
         <v>240</v>
       </c>
       <c r="B242" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D242" s="5">
         <v>-2.5454544999999999E-2</v>
@@ -5444,10 +5446,10 @@
         <v>241</v>
       </c>
       <c r="B243" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D243" s="5">
         <v>-2.5581395E-2</v>
@@ -5458,10 +5460,10 @@
         <v>242</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D244" s="5">
         <v>-2.6476578000000001E-2</v>
@@ -5472,10 +5474,10 @@
         <v>243</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D245" s="5">
         <v>-2.7619048E-2</v>
@@ -5486,10 +5488,10 @@
         <v>244</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D246" s="5">
         <v>-2.8571428999999999E-2</v>
@@ -5500,10 +5502,10 @@
         <v>245</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D247" s="5">
         <v>-2.8985507000000001E-2</v>
@@ -5514,10 +5516,10 @@
         <v>246</v>
       </c>
       <c r="B248" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D248" s="5">
         <v>-3.0555556000000001E-2</v>
@@ -5528,10 +5530,10 @@
         <v>247</v>
       </c>
       <c r="B249" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D249" s="5">
         <v>-3.125E-2</v>
@@ -5542,10 +5544,10 @@
         <v>248</v>
       </c>
       <c r="B250" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D250" s="5">
         <v>-3.1428571000000002E-2</v>
@@ -5556,10 +5558,10 @@
         <v>249</v>
       </c>
       <c r="B251" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D251" s="5">
         <v>-3.2098765000000001E-2</v>
@@ -5570,10 +5572,10 @@
         <v>250</v>
       </c>
       <c r="B252" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D252" s="5">
         <v>-3.5616438E-2</v>
@@ -5584,10 +5586,10 @@
         <v>251</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D253" s="5">
         <v>-3.7593985000000003E-2</v>
@@ -5598,10 +5600,10 @@
         <v>252</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D254" s="5">
         <v>-3.7837837999999999E-2</v>
@@ -5612,10 +5614,10 @@
         <v>253</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D255" s="5">
         <v>-3.8079469999999997E-2</v>
@@ -5626,10 +5628,10 @@
         <v>254</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D256" s="5">
         <v>-3.9393939000000003E-2</v>
@@ -5640,10 +5642,10 @@
         <v>255</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D257" s="5">
         <v>-3.9393939000000003E-2</v>
@@ -5654,10 +5656,10 @@
         <v>256</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D258" s="5">
         <v>-0.04</v>
@@ -5668,10 +5670,10 @@
         <v>257</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D259" s="5">
         <v>-0.04</v>
@@ -5682,10 +5684,10 @@
         <v>258</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D260" s="5">
         <v>-0.04</v>
@@ -5696,10 +5698,10 @@
         <v>259</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D261" s="5">
         <v>-4.0939192999999999E-2</v>
@@ -5710,10 +5712,10 @@
         <v>260</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D262" s="5">
         <v>-4.1416894000000003E-2</v>
@@ -5724,10 +5726,10 @@
         <v>261</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C263" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D263" s="5">
         <v>-4.1666666999999998E-2</v>
@@ -5738,10 +5740,10 @@
         <v>262</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D264" s="5">
         <v>-4.2285714000000002E-2</v>
@@ -5752,10 +5754,10 @@
         <v>263</v>
       </c>
       <c r="B265" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D265" s="5">
         <v>-4.2682927000000002E-2</v>
@@ -5766,10 +5768,10 @@
         <v>264</v>
       </c>
       <c r="B266" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D266" s="5">
         <v>-4.2889390999999999E-2</v>
@@ -5780,10 +5782,10 @@
         <v>265</v>
       </c>
       <c r="B267" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D267" s="5">
         <v>-4.3181817999999997E-2</v>
@@ -5794,10 +5796,10 @@
         <v>266</v>
       </c>
       <c r="B268" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D268" s="5">
         <v>-4.4559584999999999E-2</v>
@@ -5808,10 +5810,10 @@
         <v>267</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D269" s="5">
         <v>-4.516129E-2</v>
@@ -5822,10 +5824,10 @@
         <v>268</v>
       </c>
       <c r="B270" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D270" s="5">
         <v>-4.5945946000000001E-2</v>
@@ -5836,10 +5838,10 @@
         <v>269</v>
       </c>
       <c r="B271" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C271" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D271" s="5">
         <v>-0.05</v>
@@ -5850,10 +5852,10 @@
         <v>270</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D272" s="5">
         <v>-0.05</v>
@@ -5864,10 +5866,10 @@
         <v>271</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D273" s="5">
         <v>-5.0632911000000003E-2</v>
@@ -5878,10 +5880,10 @@
         <v>272</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D274" s="5">
         <v>-5.2362205000000002E-2</v>
@@ -5892,10 +5894,10 @@
         <v>273</v>
       </c>
       <c r="B275" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C275" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D275" s="5">
         <v>-5.2380952000000001E-2</v>
@@ -5906,10 +5908,10 @@
         <v>274</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D276" s="5">
         <v>-5.2631578999999998E-2</v>
@@ -5920,10 +5922,10 @@
         <v>275</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C277" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D277" s="5">
         <v>-5.2884615000000003E-2</v>
@@ -5934,10 +5936,10 @@
         <v>276</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D278" s="5">
         <v>-5.4347826000000002E-2</v>
@@ -5948,10 +5950,10 @@
         <v>277</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C279" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D279" s="5">
         <v>-5.4579792000000002E-2</v>
@@ -5962,10 +5964,10 @@
         <v>278</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D280" s="5">
         <v>-5.5555555999999999E-2</v>
@@ -5976,10 +5978,10 @@
         <v>279</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C281" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D281" s="5">
         <v>-5.5555555999999999E-2</v>
@@ -5990,10 +5992,10 @@
         <v>280</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D282" s="5">
         <v>-5.6497174999999997E-2</v>
@@ -6004,10 +6006,10 @@
         <v>281</v>
       </c>
       <c r="B283" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C283" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D283" s="5">
         <v>-5.6521739000000001E-2</v>
@@ -6018,10 +6020,10 @@
         <v>282</v>
       </c>
       <c r="B284" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D284" s="5">
         <v>-5.7542768000000001E-2</v>
@@ -6032,10 +6034,10 @@
         <v>283</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C285" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D285" s="5">
         <v>-5.8823528999999999E-2</v>
@@ -6046,10 +6048,10 @@
         <v>284</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D286" s="5">
         <v>-5.9523810000000003E-2</v>
@@ -6060,10 +6062,10 @@
         <v>285</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D287" s="5">
         <v>-6.0267857000000001E-2</v>
@@ -6074,10 +6076,10 @@
         <v>286</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D288" s="5">
         <v>-6.1538462000000002E-2</v>
@@ -6088,10 +6090,10 @@
         <v>287</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C289" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D289" s="5">
         <v>-6.3013699000000006E-2</v>
@@ -6102,10 +6104,10 @@
         <v>288</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D290" s="5">
         <v>-6.5625000000000003E-2</v>
@@ -6116,10 +6118,10 @@
         <v>289</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D291" s="5">
         <v>-6.6666666999999999E-2</v>
@@ -6130,10 +6132,10 @@
         <v>290</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D292" s="5">
         <v>-6.7326733E-2</v>
@@ -6144,10 +6146,10 @@
         <v>291</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C293" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D293" s="5">
         <v>-6.7500000000000004E-2</v>
@@ -6158,10 +6160,10 @@
         <v>292</v>
       </c>
       <c r="B294" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D294" s="5">
         <v>-6.7857142999999995E-2</v>
@@ -6172,10 +6174,10 @@
         <v>293</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D295" s="5">
         <v>-6.8243242999999995E-2</v>
@@ -6186,10 +6188,10 @@
         <v>294</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D296" s="5">
         <v>-6.9354839000000001E-2</v>
@@ -6200,10 +6202,10 @@
         <v>295</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C297" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D297" s="5">
         <v>-7.0270269999999996E-2</v>
@@ -6214,10 +6216,10 @@
         <v>296</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D298" s="5">
         <v>-7.1428570999999996E-2</v>
@@ -6228,10 +6230,10 @@
         <v>297</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D299" s="5">
         <v>-7.1755725000000006E-2</v>
@@ -6242,10 +6244,10 @@
         <v>298</v>
       </c>
       <c r="B300" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D300" s="5">
         <v>-7.1874999999999994E-2</v>
@@ -6256,10 +6258,10 @@
         <v>299</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D301" s="5">
         <v>-7.264574E-2</v>
@@ -6270,10 +6272,10 @@
         <v>300</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D302" s="5">
         <v>-7.3076923000000002E-2</v>
@@ -6284,10 +6286,10 @@
         <v>301</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D303" s="5">
         <v>-7.3557691999999994E-2</v>
@@ -6298,10 +6300,10 @@
         <v>302</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D304" s="5">
         <v>-7.3705178999999996E-2</v>
@@ -6312,10 +6314,10 @@
         <v>303</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D305" s="5">
         <v>-7.5200000000000003E-2</v>
@@ -6326,10 +6328,10 @@
         <v>304</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D306" s="5">
         <v>-7.5630251999999995E-2</v>
@@ -6340,10 +6342,10 @@
         <v>305</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D307" s="5">
         <v>-7.5862069000000004E-2</v>
@@ -6354,10 +6356,10 @@
         <v>306</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D308" s="5">
         <v>-7.5862069000000004E-2</v>
@@ -6368,10 +6370,10 @@
         <v>307</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D309" s="5">
         <v>-7.7777778000000006E-2</v>
@@ -6382,10 +6384,10 @@
         <v>308</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D310" s="5">
         <v>-7.8E-2</v>
@@ -6396,10 +6398,10 @@
         <v>309</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D311" s="5">
         <v>-7.8217822000000006E-2</v>
@@ -6410,10 +6412,10 @@
         <v>310</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D312" s="5">
         <v>-7.9245283E-2</v>
@@ -6424,10 +6426,10 @@
         <v>311</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C313" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D313" s="5">
         <v>-0.08</v>
@@ -6438,10 +6440,10 @@
         <v>312</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D314" s="5">
         <v>-0.08</v>
@@ -6452,10 +6454,10 @@
         <v>313</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D315" s="5">
         <v>-8.1081080999999999E-2</v>
@@ -6466,10 +6468,10 @@
         <v>314</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D316" s="5">
         <v>-8.3870968000000004E-2</v>
@@ -6480,10 +6482,10 @@
         <v>315</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D317" s="5">
         <v>-8.4732823999999998E-2</v>
@@ -6494,10 +6496,10 @@
         <v>316</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D318" s="5">
         <v>-8.4967319999999999E-2</v>
@@ -6508,10 +6510,10 @@
         <v>317</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D319" s="5">
         <v>-8.5365854000000005E-2</v>
@@ -6522,10 +6524,10 @@
         <v>318</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D320" s="5">
         <v>-8.6567164000000002E-2</v>
@@ -6536,10 +6538,10 @@
         <v>319</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D321" s="5">
         <v>-8.6956521999999994E-2</v>
@@ -6550,10 +6552,10 @@
         <v>320</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D322" s="5">
         <v>-8.7330317000000005E-2</v>
@@ -6564,10 +6566,10 @@
         <v>321</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D323" s="5">
         <v>-8.9956332E-2</v>
@@ -6578,10 +6580,10 @@
         <v>322</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D324" s="5">
         <v>-9.0163934000000001E-2</v>
@@ -6592,10 +6594,10 @@
         <v>323</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D325" s="5">
         <v>-9.0909090999999997E-2</v>
@@ -6606,10 +6608,10 @@
         <v>324</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D326" s="5">
         <v>-9.1999999999999998E-2</v>
@@ -6620,10 +6622,10 @@
         <v>325</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D327" s="5">
         <v>-9.2957745999999994E-2</v>
@@ -6634,10 +6636,10 @@
         <v>326</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D328" s="5">
         <v>-9.4470046000000002E-2</v>
@@ -6648,10 +6650,10 @@
         <v>327</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D329" s="5">
         <v>-9.5652174000000006E-2</v>
@@ -6662,10 +6664,10 @@
         <v>328</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D330" s="5">
         <v>-9.5890410999999995E-2</v>
@@ -6676,10 +6678,10 @@
         <v>329</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D331" s="5">
         <v>-9.6296296000000003E-2</v>
@@ -6690,10 +6692,10 @@
         <v>330</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D332" s="5">
         <v>-9.6296296000000003E-2</v>
@@ -6704,10 +6706,10 @@
         <v>331</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D333" s="5">
         <v>-9.6666666999999998E-2</v>
@@ -6718,10 +6720,10 @@
         <v>332</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D334" s="5">
         <v>-9.8461538000000001E-2</v>
@@ -6732,10 +6734,10 @@
         <v>333</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D335" s="5">
         <v>-9.8529411999999997E-2</v>
@@ -6746,10 +6748,10 @@
         <v>334</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D336" s="5">
         <v>-0.1</v>
@@ -6760,10 +6762,10 @@
         <v>335</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D337" s="5">
         <v>-0.1</v>
@@ -6774,10 +6776,10 @@
         <v>336</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D338" s="5">
         <v>-0.1</v>
@@ -6788,10 +6790,10 @@
         <v>337</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D339" s="5">
         <v>-0.1</v>
@@ -6802,10 +6804,10 @@
         <v>338</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D340" s="5">
         <v>-0.102941176</v>
@@ -6816,10 +6818,10 @@
         <v>339</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D341" s="5">
         <v>-0.104545455</v>
@@ -6830,10 +6832,10 @@
         <v>340</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D342" s="5">
         <v>-0.104545455</v>
@@ -6844,10 +6846,10 @@
         <v>341</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D343" s="5">
         <v>-0.105</v>
@@ -6858,10 +6860,10 @@
         <v>342</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D344" s="5">
         <v>-0.105882353</v>
@@ -6872,10 +6874,10 @@
         <v>343</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D345" s="5">
         <v>-0.109659091</v>
@@ -6886,10 +6888,10 @@
         <v>344</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D346" s="5">
         <v>-0.10994475099999999</v>
@@ -6900,10 +6902,10 @@
         <v>345</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D347" s="5">
         <v>-0.111111111</v>
@@ -6914,10 +6916,10 @@
         <v>346</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D348" s="5">
         <v>-0.112222222</v>
@@ -6928,10 +6930,10 @@
         <v>347</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D349" s="5">
         <v>-0.1125</v>
@@ -6942,10 +6944,10 @@
         <v>348</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D350" s="5">
         <v>-0.11353711800000001</v>
@@ -6956,10 +6958,10 @@
         <v>349</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D351" s="5">
         <v>-0.113559322</v>
@@ -6970,10 +6972,10 @@
         <v>350</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D352" s="5">
         <v>-0.113636364</v>
@@ -6984,10 +6986,10 @@
         <v>351</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D353" s="5">
         <v>-0.115384615</v>
@@ -6998,10 +7000,10 @@
         <v>352</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D354" s="5">
         <v>-0.115789474</v>
@@ -7012,10 +7014,10 @@
         <v>353</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D355" s="5">
         <v>-0.117346939</v>
@@ -7026,10 +7028,10 @@
         <v>354</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D356" s="5">
         <v>-0.118897638</v>
@@ -7040,10 +7042,10 @@
         <v>355</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D357" s="5">
         <v>-0.12074235799999999</v>
@@ -7054,10 +7056,10 @@
         <v>356</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D358" s="5">
         <v>-0.122173913</v>
@@ -7068,10 +7070,10 @@
         <v>357</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D359" s="5">
         <v>-0.122580645</v>
@@ -7082,10 +7084,10 @@
         <v>358</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D360" s="5">
         <v>-0.123308271</v>
@@ -7096,10 +7098,10 @@
         <v>359</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D361" s="5">
         <v>-0.125</v>
@@ -7110,10 +7112,10 @@
         <v>360</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D362" s="5">
         <v>-0.125892857</v>
@@ -7124,10 +7126,10 @@
         <v>361</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D363" s="5">
         <v>-0.126618705</v>
@@ -7138,10 +7140,10 @@
         <v>362</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D364" s="5">
         <v>-0.127272727</v>
@@ -7152,10 +7154,10 @@
         <v>363</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D365" s="5">
         <v>-0.128</v>
@@ -7166,10 +7168,10 @@
         <v>364</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D366" s="5">
         <v>-0.12830882399999999</v>
@@ -7180,10 +7182,10 @@
         <v>365</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D367" s="5">
         <v>-0.12857142899999999</v>
@@ -7194,10 +7196,10 @@
         <v>366</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D368" s="5">
         <v>-0.12875</v>
@@ -7208,10 +7210,10 @@
         <v>367</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D369" s="5">
         <v>-0.12989130400000001</v>
@@ -7222,10 +7224,10 @@
         <v>368</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D370" s="5">
         <v>-0.13013698600000001</v>
@@ -7236,10 +7238,10 @@
         <v>369</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D371" s="5">
         <v>-0.133333333</v>
@@ -7250,10 +7252,10 @@
         <v>370</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D372" s="5">
         <v>-0.13345195700000001</v>
@@ -7264,10 +7266,10 @@
         <v>371</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D373" s="5">
         <v>-0.13445378199999999</v>
@@ -7278,10 +7280,10 @@
         <v>372</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D374" s="5">
         <v>-0.13684210499999999</v>
@@ -7292,10 +7294,10 @@
         <v>373</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D375" s="5">
         <v>-0.13750000000000001</v>
@@ -7306,10 +7308,10 @@
         <v>374</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D376" s="5">
         <v>-0.138461538</v>
@@ -7320,10 +7322,10 @@
         <v>375</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D377" s="5">
         <v>-0.140625</v>
@@ -7334,10 +7336,10 @@
         <v>376</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D378" s="5">
         <v>-0.14104046200000001</v>
@@ -7348,10 +7350,10 @@
         <v>377</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D379" s="5">
         <v>-0.14230769200000001</v>
@@ -7362,10 +7364,10 @@
         <v>378</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D380" s="5">
         <v>-0.14230769200000001</v>
@@ -7376,10 +7378,10 @@
         <v>379</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D381" s="5">
         <v>-0.14285714299999999</v>
@@ -7390,10 +7392,10 @@
         <v>380</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D382" s="5">
         <v>-0.14313725499999999</v>
@@ -7404,10 +7406,10 @@
         <v>381</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D383" s="5">
         <v>-0.14461538500000001</v>
@@ -7418,10 +7420,10 @@
         <v>382</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D384" s="5">
         <v>-0.144736842</v>
@@ -7432,10 +7434,10 @@
         <v>383</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D385" s="5">
         <v>-0.14516129</v>
@@ -7446,10 +7448,10 @@
         <v>384</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D386" s="5">
         <v>-0.14545454499999999</v>
@@ -7460,10 +7462,10 @@
         <v>385</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D387" s="5">
         <v>-0.14724409399999999</v>
@@ -7474,10 +7476,10 @@
         <v>386</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D388" s="5">
         <v>-0.15</v>
@@ -7488,10 +7490,10 @@
         <v>387</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D389" s="5">
         <v>-0.15084745799999999</v>
@@ -7502,10 +7504,10 @@
         <v>388</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D390" s="5">
         <v>-0.15099337700000001</v>
@@ -7516,10 +7518,10 @@
         <v>389</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D391" s="5">
         <v>-0.15116279099999999</v>
@@ -7530,10 +7532,10 @@
         <v>390</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D392" s="5">
         <v>-0.15131578900000001</v>
@@ -7544,10 +7546,10 @@
         <v>391</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D393" s="5">
         <v>-0.15263157899999999</v>
@@ -7558,10 +7560,10 @@
         <v>392</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D394" s="5">
         <v>-0.15284974100000001</v>
@@ -7572,10 +7574,10 @@
         <v>393</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D395" s="5">
         <v>-0.15294117600000001</v>
@@ -7586,10 +7588,10 @@
         <v>394</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D396" s="5">
         <v>-0.15862069000000001</v>
@@ -7600,10 +7602,10 @@
         <v>395</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D397" s="5">
         <v>-0.15979381400000001</v>
@@ -7614,10 +7616,10 @@
         <v>396</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D398" s="5">
         <v>-0.16126760600000001</v>
@@ -7628,10 +7630,10 @@
         <v>397</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D399" s="5">
         <v>-0.167567568</v>
@@ -7642,10 +7644,10 @@
         <v>398</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D400" s="5">
         <v>-0.17111111100000001</v>
@@ -7656,10 +7658,10 @@
         <v>399</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D401" s="5">
         <v>-0.17173912999999999</v>
@@ -7670,10 +7672,10 @@
         <v>400</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D402" s="5">
         <v>-0.17236842099999999</v>
@@ -7684,10 +7686,10 @@
         <v>401</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D403" s="5">
         <v>-0.172839506</v>
@@ -7698,10 +7700,10 @@
         <v>402</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D404" s="5">
         <v>-0.173626374</v>
@@ -7712,10 +7714,10 @@
         <v>403</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D405" s="5">
         <v>-0.173626374</v>
@@ -7726,10 +7728,10 @@
         <v>404</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D406" s="5">
         <v>-0.175257732</v>
@@ -7740,10 +7742,10 @@
         <v>405</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D407" s="5">
         <v>-0.18181818199999999</v>
@@ -7754,10 +7756,10 @@
         <v>406</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D408" s="5">
         <v>-0.18279569900000001</v>
@@ -7768,10 +7770,10 @@
         <v>407</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D409" s="5">
         <v>-0.18378378400000001</v>
@@ -7782,10 +7784,10 @@
         <v>408</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D410" s="5">
         <v>-0.18389261700000001</v>
@@ -7796,10 +7798,10 @@
         <v>409</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D411" s="5">
         <v>-0.184246575</v>
@@ -7810,10 +7812,10 @@
         <v>410</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D412" s="5">
         <v>-0.185365854</v>
@@ -7824,10 +7826,10 @@
         <v>411</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D413" s="5">
         <v>-0.18723404299999999</v>
@@ -7838,10 +7840,10 @@
         <v>412</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D414" s="5">
         <v>-0.1875</v>
@@ -7852,10 +7854,10 @@
         <v>413</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D415" s="5">
         <v>-0.188</v>
@@ -7866,10 +7868,10 @@
         <v>414</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D416" s="5">
         <v>-0.18983050800000001</v>
@@ -7880,10 +7882,10 @@
         <v>415</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D417" s="5">
         <v>-0.18983050800000001</v>
@@ -7894,10 +7896,10 @@
         <v>416</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D418" s="5">
         <v>-0.19047618999999999</v>
@@ -7908,10 +7910,10 @@
         <v>417</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D419" s="5">
         <v>-0.19047618999999999</v>
@@ -7922,10 +7924,10 @@
         <v>418</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D420" s="5">
         <v>-0.19463087200000001</v>
@@ -7936,10 +7938,10 @@
         <v>419</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D421" s="5">
         <v>-0.2</v>
@@ -7950,10 +7952,10 @@
         <v>420</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D422" s="5">
         <v>-0.2</v>
@@ -7964,10 +7966,10 @@
         <v>421</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D423" s="5">
         <v>-0.20266666699999999</v>
@@ -7978,10 +7980,10 @@
         <v>422</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D424" s="5">
         <v>-0.21136363599999999</v>
@@ -7992,10 +7994,10 @@
         <v>423</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D425" s="5">
         <v>-0.213636364</v>
@@ -8006,10 +8008,10 @@
         <v>424</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D426" s="5">
         <v>-0.21621621599999999</v>
@@ -8020,10 +8022,10 @@
         <v>425</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D427" s="5">
         <v>-0.21666666700000001</v>
@@ -8034,10 +8036,10 @@
         <v>426</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D428" s="5">
         <v>-0.21856287399999999</v>
@@ -8048,10 +8050,10 @@
         <v>427</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D429" s="5">
         <v>-0.220930233</v>
@@ -8062,10 +8064,10 @@
         <v>428</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D430" s="5">
         <v>-0.222222222</v>
@@ -8076,10 +8078,10 @@
         <v>429</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D431" s="5">
         <v>-0.22264150899999999</v>
@@ -8090,10 +8092,10 @@
         <v>430</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D432" s="5">
         <v>-0.22384106000000001</v>
@@ -8104,10 +8106,10 @@
         <v>431</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D433" s="5">
         <v>-0.22459016400000001</v>
@@ -8118,10 +8120,10 @@
         <v>432</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D434" s="5">
         <v>-0.22500000000000001</v>
@@ -8132,10 +8134,10 @@
         <v>433</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D435" s="5">
         <v>-0.22666666699999999</v>
@@ -8146,10 +8148,10 @@
         <v>434</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D436" s="5">
         <v>-0.227210884</v>
@@ -8160,10 +8162,10 @@
         <v>435</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D437" s="5">
         <v>-0.22830188700000001</v>
@@ -8174,10 +8176,10 @@
         <v>436</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D438" s="5">
         <v>-0.25</v>
@@ -8188,10 +8190,10 @@
         <v>437</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D439" s="5">
         <v>-0.25</v>
@@ -8202,10 +8204,10 @@
         <v>438</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D440" s="5">
         <v>-0.251923077</v>
@@ -8216,10 +8218,10 @@
         <v>439</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D441" s="5">
         <v>-0.257142857</v>
@@ -8230,10 +8232,10 @@
         <v>440</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D442" s="5">
         <v>-0.257352941</v>
@@ -8244,10 +8246,10 @@
         <v>441</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D443" s="5">
         <v>-0.25806451600000002</v>
@@ -8258,10 +8260,10 @@
         <v>442</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D444" s="5">
         <v>-0.26057298800000001</v>
@@ -8272,10 +8274,10 @@
         <v>443</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D445" s="5">
         <v>-0.26114649699999998</v>
@@ -8286,10 +8288,10 @@
         <v>444</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D446" s="5">
         <v>-0.26666666700000002</v>
@@ -8300,10 +8302,10 @@
         <v>445</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D447" s="5">
         <v>-0.27272727299999999</v>
@@ -8314,10 +8316,10 @@
         <v>446</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D448" s="5">
         <v>-0.27636363600000002</v>
@@ -8328,10 +8330,10 @@
         <v>447</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D449" s="5">
         <v>-0.27777777799999998</v>
@@ -8342,10 +8344,10 @@
         <v>448</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D450" s="5">
         <v>-0.28313252999999999</v>
@@ -8356,10 +8358,10 @@
         <v>449</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D451" s="5">
         <v>-0.28999999999999998</v>
@@ -8370,10 +8372,10 @@
         <v>450</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D452" s="5">
         <v>-0.29166666699999999</v>
@@ -8384,10 +8386,10 @@
         <v>451</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D453" s="5">
         <v>-0.29599999999999999</v>
@@ -8398,10 +8400,10 @@
         <v>452</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D454" s="5">
         <v>-0.32297154900000002</v>
@@ -8412,10 +8414,10 @@
         <v>453</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D455" s="5">
         <v>-0.32500000000000001</v>
@@ -8426,10 +8428,10 @@
         <v>454</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D456" s="5">
         <v>-0.33714285700000002</v>
@@ -8440,10 +8442,10 @@
         <v>455</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D457" s="5">
         <v>-0.33823529400000002</v>
@@ -8454,10 +8456,10 @@
         <v>456</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D458" s="5">
         <v>-0.34399999999999997</v>
@@ -8468,10 +8470,10 @@
         <v>457</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D459" s="5">
         <v>-0.35284552800000002</v>
@@ -8482,10 +8484,10 @@
         <v>458</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D460" s="5">
         <v>-0.35504886000000002</v>
@@ -8496,10 +8498,10 @@
         <v>459</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D461" s="5">
         <v>-0.35584989</v>
@@ -8510,10 +8512,10 @@
         <v>460</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D462" s="5">
         <v>-0.38265895999999999</v>
@@ -8524,10 +8526,10 @@
         <v>461</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D463" s="5">
         <v>-0.39055793999999999</v>
@@ -8538,10 +8540,10 @@
         <v>462</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D464" s="5">
         <v>-0.39303797499999998</v>
@@ -8552,10 +8554,10 @@
         <v>463</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D465" s="5">
         <v>-0.39701492500000002</v>
@@ -8566,10 +8568,10 @@
         <v>464</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D466" s="5">
         <v>-0.41269841299999999</v>
@@ -8580,10 +8582,10 @@
         <v>465</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D467" s="5">
         <v>-0.43727272700000003</v>
@@ -8594,10 +8596,10 @@
         <v>466</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D468" s="5">
         <v>-0.44927536200000001</v>
@@ -8608,10 +8610,10 @@
         <v>467</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D469" s="5">
         <v>-0.45121951199999999</v>
@@ -8622,10 +8624,10 @@
         <v>468</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D470" s="5">
         <v>-0.45299145299999999</v>
@@ -8636,10 +8638,10 @@
         <v>469</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D471" s="5">
         <v>-0.453125</v>
@@ -8650,10 +8652,10 @@
         <v>470</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D472" s="5">
         <v>-0.46153846199999998</v>
@@ -8664,10 +8666,10 @@
         <v>471</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D473" s="5">
         <v>-0.47631578899999999</v>
@@ -8678,10 +8680,10 @@
         <v>472</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D474" s="5">
         <v>-0.48</v>
@@ -8692,10 +8694,10 @@
         <v>473</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D475" s="5">
         <v>-0.48965517200000003</v>
@@ -8706,10 +8708,10 @@
         <v>474</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D476" s="5">
         <v>-0.5</v>
@@ -8720,10 +8722,10 @@
         <v>475</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D477" s="5">
         <v>-0.56597222199999997</v>
@@ -8734,10 +8736,10 @@
         <v>476</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D478" s="5">
         <v>-0.58260869599999998</v>
@@ -8748,10 +8750,10 @@
         <v>477</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D479" s="5">
         <v>-0.592307692</v>
@@ -8762,10 +8764,10 @@
         <v>478</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D480" s="5">
         <v>-0.59638554200000005</v>
@@ -8776,10 +8778,10 @@
         <v>479</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D481" s="5">
         <v>-0.67307692299999999</v>
@@ -8790,10 +8792,10 @@
         <v>480</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D482" s="5">
         <v>-0.7</v>
@@ -8804,10 +8806,10 @@
         <v>481</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D483" s="5">
         <v>-0.7</v>
@@ -8818,10 +8820,10 @@
         <v>482</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D484" s="5">
         <v>-0.73333333300000003</v>
@@ -8832,10 +8834,10 @@
         <v>483</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D485" s="5">
         <v>-0.73333333300000003</v>
@@ -8846,10 +8848,10 @@
         <v>484</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D486" s="5">
         <v>-0.8</v>
@@ -8860,10 +8862,10 @@
         <v>485</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D487" s="5">
         <v>-0.8</v>
@@ -8874,10 +8876,10 @@
         <v>486</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D488" s="5">
         <v>-0.82926829300000005</v>
@@ -8888,10 +8890,10 @@
         <v>487</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D489" s="5">
         <v>-0.83333333300000001</v>
@@ -8902,10 +8904,10 @@
         <v>488</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D490" s="5">
         <v>-0.87179487200000005</v>
@@ -8916,10 +8918,10 @@
         <v>489</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D491" s="5">
         <v>-0.93333333299999999</v>
@@ -8930,10 +8932,10 @@
         <v>490</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D492" s="5">
         <v>-0.99333333300000004</v>
@@ -8944,10 +8946,10 @@
         <v>491</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D493" s="5">
         <v>-1.3333333329999999</v>
@@ -8958,10 +8960,10 @@
         <v>492</v>
       </c>
       <c r="B494" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C494" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D494" s="5">
         <v>-1.4</v>
@@ -8972,10 +8974,10 @@
         <v>493</v>
       </c>
       <c r="B495" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C495" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D495" s="5">
         <v>-1.907142857</v>
@@ -8986,10 +8988,10 @@
         <v>494</v>
       </c>
       <c r="B496" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C496" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D496" s="5">
         <v>-2.1</v>
@@ -9000,10 +9002,10 @@
         <v>495</v>
       </c>
       <c r="B497" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C497" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D497" s="5">
         <v>-2.75</v>
@@ -9030,21 +9032,21 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>9</v>
-      </c>
       <c r="D2" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>509</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>510</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>1</v>
@@ -9055,13 +9057,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>511</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>512</v>
       </c>
       <c r="E3" s="4">
         <v>215</v>
@@ -9075,13 +9077,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>513</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>514</v>
       </c>
       <c r="E4" s="4">
         <v>170</v>
@@ -9095,13 +9097,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>515</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>516</v>
       </c>
       <c r="E5" s="4">
         <v>150</v>
@@ -9115,13 +9117,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>517</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>518</v>
       </c>
       <c r="E6" s="4">
         <v>86</v>
@@ -9135,13 +9137,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="E7" s="4">
         <v>74</v>
